--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,51 +674,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -820,7 +816,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -828,51 +824,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -983,7 +975,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -1017,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1094,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1124,7 +1116,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1132,47 +1124,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1197,7 +1193,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1205,8 +1201,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1215,37 +1213,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1278,47 +1278,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>2</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1390,12 +1394,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1429,11 +1433,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1463,12 +1467,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1540,12 +1544,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1579,11 +1583,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1613,12 +1617,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1643,7 +1647,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1651,10 +1655,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1663,39 +1665,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1729,11 +1729,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1879,11 +1879,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2029,11 +2029,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2179,11 +2179,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2329,11 +2329,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2551,8 +2551,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2561,37 +2563,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2663,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2689,7 +2693,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2697,47 +2701,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2771,7 +2779,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2805,12 +2813,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2835,7 +2843,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2843,8 +2851,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>1</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2853,37 +2863,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2917,11 +2929,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2951,12 +2963,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2992,9 +3004,9 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3024,12 +3036,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3063,11 +3075,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3097,12 +3109,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3136,11 +3148,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3170,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3209,11 +3221,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3231,7 +3243,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3243,12 +3255,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3282,7 +3294,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3316,12 +3328,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3357,9 +3369,9 @@
       <c r="I39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3389,12 +3401,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3430,9 +3442,9 @@
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3462,12 +3474,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3501,7 +3513,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3535,12 +3547,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3574,7 +3586,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3608,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3638,7 +3650,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3646,51 +3658,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3726,9 +3734,9 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3758,12 +3766,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3797,7 +3805,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3831,12 +3839,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3870,11 +3878,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3904,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3945,9 +3953,9 @@
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3977,12 +3985,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4016,11 +4024,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4050,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4080,7 +4088,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4088,47 +4096,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4162,11 +4174,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4196,12 +4208,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4235,11 +4247,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4269,12 +4281,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4342,12 +4354,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4381,11 +4393,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4415,12 +4427,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4458,7 +4470,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4488,12 +4500,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4529,9 +4541,9 @@
       <c r="I55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4561,12 +4573,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4600,11 +4612,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4634,12 +4646,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4673,11 +4685,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4695,7 +4707,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4707,12 +4719,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4750,7 +4762,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4780,12 +4792,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4821,9 +4833,9 @@
       <c r="I59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4853,12 +4865,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4892,7 +4904,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4926,12 +4938,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4965,11 +4977,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4999,12 +5011,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5072,12 +5084,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5113,9 +5125,9 @@
       <c r="I63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5133,7 +5145,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5145,12 +5157,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5184,11 +5196,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5218,12 +5230,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5257,11 +5269,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5279,7 +5291,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5291,12 +5303,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5330,7 +5342,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5364,12 +5376,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5403,11 +5415,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5437,12 +5449,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5510,12 +5522,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5551,9 +5563,9 @@
       <c r="I69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5583,12 +5595,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5622,7 +5634,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5656,12 +5668,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5695,11 +5707,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5717,7 +5729,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5729,12 +5741,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5768,7 +5780,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5802,12 +5814,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5841,11 +5853,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5875,12 +5887,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5948,12 +5960,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5991,7 +6003,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6021,12 +6033,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6064,7 +6076,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6094,78 +6106,516 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-022-CZ</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Lixeira Preto com Cinza</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>5929841586</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>R$ 49,90</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,14 +636,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -827,9 +827,9 @@
       <c r="I5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,14 +936,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -975,11 +975,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,14 +1086,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1124,10 +1124,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1136,39 +1134,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1240,12 +1236,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1317,12 +1313,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1394,14 +1390,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1424,7 +1420,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1432,8 +1428,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1442,37 +1440,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1544,14 +1544,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1585,9 +1585,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1617,14 +1617,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1655,8 +1655,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1665,39 +1667,41 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1729,11 +1733,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1763,14 +1767,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1793,7 +1797,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1801,10 +1805,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1813,39 +1815,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1881,9 +1881,9 @@
       <c r="I19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1990,14 +1990,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2029,11 +2029,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2290,14 +2290,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2329,11 +2329,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2440,14 +2440,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2479,11 +2479,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2590,14 +2590,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2629,11 +2629,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2740,14 +2740,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2779,11 +2779,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2963,14 +2963,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3001,8 +3001,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3011,39 +3013,41 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3075,11 +3079,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3109,14 +3113,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3150,9 +3154,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3182,14 +3186,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3221,11 +3225,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3255,14 +3259,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3294,11 +3298,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3328,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3369,9 +3373,9 @@
       <c r="I39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3401,14 +3405,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3440,11 +3444,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3474,14 +3478,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3513,11 +3517,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3547,14 +3551,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3586,11 +3590,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3620,14 +3624,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3659,11 +3663,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3681,7 +3685,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3693,14 +3697,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3732,7 +3736,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3766,14 +3770,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3805,11 +3809,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3827,7 +3831,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3839,12 +3843,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3912,14 +3916,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3951,7 +3955,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3985,12 +3989,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4058,14 +4062,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4096,10 +4100,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4108,41 +4110,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4176,9 +4176,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4208,14 +4208,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4246,8 +4246,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4256,39 +4258,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4320,11 +4324,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4354,14 +4358,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4395,9 +4399,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4427,12 +4431,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4500,14 +4504,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4539,11 +4543,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4573,12 +4577,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4646,14 +4650,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4685,11 +4689,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4719,12 +4723,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4792,14 +4796,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4831,11 +4835,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4865,12 +4869,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4908,7 +4912,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4938,12 +4942,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5011,14 +5015,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5050,11 +5054,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5084,12 +5088,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5145,7 +5149,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5157,14 +5161,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5196,11 +5200,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5230,12 +5234,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5271,9 +5275,9 @@
       <c r="I65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5291,7 +5295,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5303,14 +5307,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5342,7 +5346,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5376,14 +5380,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5415,11 +5419,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5449,14 +5453,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5490,9 +5494,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5522,14 +5526,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5561,11 +5565,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5595,14 +5599,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5634,11 +5638,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5668,14 +5672,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5707,11 +5711,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5729,7 +5733,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5741,12 +5745,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5784,7 +5788,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5814,14 +5818,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5853,11 +5857,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5875,7 +5879,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5887,14 +5891,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5926,11 +5930,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5960,14 +5964,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5999,11 +6003,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6033,14 +6037,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6072,11 +6076,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6106,12 +6110,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6149,7 +6153,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6179,12 +6183,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6222,7 +6226,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6252,14 +6256,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6291,11 +6295,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6325,14 +6329,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6364,11 +6368,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6398,14 +6402,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6437,11 +6441,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6471,14 +6475,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6510,11 +6514,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6544,78 +6548,224 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-022-CZ</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Lixeira Preto com Cinza</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>5929841586</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>R$ 49,90</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -975,11 +975,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1127,9 +1127,9 @@
       <c r="I9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1274,51 +1274,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1390,12 +1386,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1420,7 +1416,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1428,51 +1424,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1544,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1583,7 +1575,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1617,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1694,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1724,7 +1716,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1732,47 +1724,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1805,8 +1801,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1815,37 +1813,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1878,47 +1878,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>2</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1990,12 +1994,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2029,11 +2033,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2063,12 +2067,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2140,12 +2144,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2179,11 +2183,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2213,12 +2217,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2243,7 +2247,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2251,10 +2255,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2263,39 +2265,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2329,11 +2329,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2479,11 +2479,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2629,11 +2629,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2779,11 +2779,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2929,11 +2929,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3113,12 +3113,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3151,8 +3151,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3161,37 +3163,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3227,7 +3231,7 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -3259,12 +3263,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3289,7 +3293,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3297,47 +3301,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3371,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3405,12 +3413,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3435,7 +3443,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3443,8 +3451,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>1</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3453,37 +3463,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3517,11 +3529,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3551,12 +3563,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3592,9 +3604,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3624,12 +3636,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3663,11 +3675,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3697,12 +3709,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3736,11 +3748,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3770,12 +3782,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3809,11 +3821,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3831,7 +3843,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3843,12 +3855,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3882,7 +3894,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3916,12 +3928,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3957,9 +3969,9 @@
       <c r="I47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3989,12 +4001,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4030,9 +4042,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4062,12 +4074,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4101,7 +4113,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4135,12 +4147,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4174,7 +4186,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4208,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4238,7 +4250,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4246,51 +4258,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4326,9 +4334,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4358,12 +4366,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4397,7 +4405,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4431,12 +4439,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4470,11 +4478,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4504,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4545,9 +4553,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4577,12 +4585,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4616,11 +4624,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4650,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4680,7 +4688,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4688,47 +4696,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4762,11 +4774,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4796,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4835,11 +4847,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4869,12 +4881,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4942,12 +4954,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4981,11 +4993,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5015,12 +5027,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5058,7 +5070,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5088,12 +5100,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5129,9 +5141,9 @@
       <c r="I63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5161,12 +5173,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5200,11 +5212,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5234,12 +5246,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5273,11 +5285,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5295,7 +5307,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5307,12 +5319,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5350,7 +5362,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5380,12 +5392,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5421,9 +5433,9 @@
       <c r="I67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5453,12 +5465,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5492,7 +5504,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5526,12 +5538,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5565,11 +5577,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5599,12 +5611,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5640,7 +5652,7 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5672,12 +5684,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5713,9 +5725,9 @@
       <c r="I71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5733,7 +5745,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5745,12 +5757,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5784,11 +5796,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5818,12 +5830,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5857,11 +5869,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5879,7 +5891,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5891,12 +5903,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5930,7 +5942,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5964,12 +5976,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6003,11 +6015,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6037,12 +6049,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6078,7 +6090,7 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6110,12 +6122,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6151,9 +6163,9 @@
       <c r="I77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6183,12 +6195,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6222,7 +6234,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6256,12 +6268,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6295,11 +6307,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6317,7 +6329,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6329,12 +6341,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6368,7 +6380,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6402,12 +6414,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6441,11 +6453,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6475,12 +6487,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6516,7 +6528,7 @@
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="4" t="inlineStr">
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6548,12 +6560,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6591,7 +6603,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6621,12 +6633,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6664,7 +6676,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6694,78 +6706,516 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-022-CZ</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Lixeira Preto com Cinza</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>5929841586</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>R$ 49,90</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,47 +674,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,7 +820,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -824,8 +828,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>2</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -834,37 +840,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -977,9 +985,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1009,12 +1017,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1094,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1125,11 +1133,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1159,12 +1167,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1236,12 +1244,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1275,11 +1283,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1309,12 +1317,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1386,12 +1394,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1425,11 +1433,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1459,12 +1467,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1536,12 +1544,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1577,9 +1585,9 @@
       <c r="I15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1609,12 +1617,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1686,12 +1694,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1716,7 +1724,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1724,51 +1732,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1840,12 +1844,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1870,7 +1874,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1878,51 +1882,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2067,12 +2067,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2182,47 +2182,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2247,7 +2251,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2255,8 +2259,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2265,37 +2271,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2320,7 +2328,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2328,47 +2336,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>2</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2440,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2479,11 +2491,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2513,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2590,12 +2602,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2629,11 +2641,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2663,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2693,7 +2705,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2701,10 +2713,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2713,39 +2723,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2779,11 +2787,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2813,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2890,12 +2898,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2929,11 +2937,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2963,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3040,12 +3048,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3079,11 +3087,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3113,12 +3121,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3190,12 +3198,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3229,11 +3237,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3263,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3340,12 +3348,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3379,11 +3387,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3413,12 +3421,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3490,12 +3498,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3563,12 +3571,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3593,7 +3601,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3601,8 +3609,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3611,37 +3621,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,12 +3721,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3739,7 +3751,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3747,47 +3759,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3821,7 +3837,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3855,12 +3871,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3885,7 +3901,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3893,8 +3909,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>1</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3903,37 +3921,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3967,11 +3987,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -4001,12 +4021,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4042,9 +4062,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4074,12 +4094,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4113,11 +4133,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4147,12 +4167,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4186,11 +4206,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4220,12 +4240,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4259,11 +4279,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4281,7 +4301,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4293,12 +4313,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4332,7 +4352,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4366,12 +4386,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4407,9 +4427,9 @@
       <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4439,12 +4459,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4480,9 +4500,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4512,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4551,7 +4571,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4585,12 +4605,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4624,7 +4644,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4658,12 +4678,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4688,7 +4708,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4696,51 +4716,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4776,9 +4792,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4808,12 +4824,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4847,7 +4863,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4881,12 +4897,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4920,11 +4936,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4954,12 +4970,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4995,9 +5011,9 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5027,12 +5043,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5066,11 +5082,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5100,12 +5116,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5130,7 +5146,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5138,47 +5154,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5212,11 +5232,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5246,12 +5266,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5285,11 +5305,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5319,12 +5339,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5392,12 +5412,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5431,11 +5451,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5465,12 +5485,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5508,7 +5528,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5538,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5579,9 +5599,9 @@
       <c r="I69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5611,12 +5631,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5650,11 +5670,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5684,12 +5704,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5723,11 +5743,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5745,7 +5765,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5757,12 +5777,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5800,7 +5820,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5830,12 +5850,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5871,9 +5891,9 @@
       <c r="I73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5903,12 +5923,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5942,7 +5962,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5976,12 +5996,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6015,11 +6035,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6049,12 +6069,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6122,12 +6142,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6163,9 +6183,9 @@
       <c r="I77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6183,7 +6203,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6195,12 +6215,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6234,11 +6254,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6268,12 +6288,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6307,11 +6327,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6329,7 +6349,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6341,12 +6361,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6380,7 +6400,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6414,12 +6434,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6453,11 +6473,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6487,12 +6507,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6560,12 +6580,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6601,9 +6621,9 @@
       <c r="I83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6633,12 +6653,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6672,7 +6692,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6706,12 +6726,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6745,11 +6765,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6767,7 +6787,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6779,12 +6799,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6818,7 +6838,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6852,12 +6872,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6891,11 +6911,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6925,12 +6945,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6998,12 +7018,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7041,7 +7061,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7071,12 +7091,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7114,7 +7134,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7144,78 +7164,516 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-022-CZ</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Lixeira Preto com Cinza</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>5929841586</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>R$ 49,90</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,14 +944,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -974,7 +974,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -982,8 +982,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -992,37 +994,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1094,14 +1098,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1135,9 +1139,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1167,12 +1171,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1244,14 +1248,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1283,11 +1287,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1317,12 +1321,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1394,14 +1398,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1433,11 +1437,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1467,12 +1471,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1544,14 +1548,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1583,11 +1587,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1617,12 +1621,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1694,14 +1698,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -1733,11 +1737,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1767,12 +1771,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1844,12 +1848,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1885,9 +1889,9 @@
       <c r="I19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1917,12 +1921,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1994,14 +1998,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2033,11 +2037,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2067,12 +2071,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2144,14 +2148,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2174,7 +2178,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2182,10 +2186,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2194,39 +2196,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,14 +2452,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2490,8 +2490,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2500,37 +2502,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,14 +2606,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2643,9 +2647,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2675,14 +2679,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2705,7 +2709,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2713,8 +2717,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2723,39 +2729,41 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2787,11 +2795,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2821,14 +2829,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -2851,7 +2859,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2859,10 +2867,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2871,39 +2877,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2939,9 +2943,9 @@
       <c r="I33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2971,12 +2975,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3048,14 +3052,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3087,11 +3091,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3121,12 +3125,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3198,12 +3202,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3241,7 +3245,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3271,12 +3275,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3348,14 +3352,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3387,11 +3391,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3421,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3498,14 +3502,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3537,11 +3541,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3571,12 +3575,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3648,14 +3652,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3687,11 +3691,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3721,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3798,14 +3802,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -3837,11 +3841,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3871,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3948,12 +3952,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3991,7 +3995,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -4021,14 +4025,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4051,7 +4055,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4059,8 +4063,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4069,39 +4075,41 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4133,11 +4141,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4167,14 +4175,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4208,9 +4216,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4240,14 +4248,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4279,11 +4287,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4313,14 +4321,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4352,11 +4360,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4386,12 +4394,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4427,9 +4435,9 @@
       <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4459,14 +4467,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4498,11 +4506,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4532,14 +4540,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4571,11 +4579,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4605,14 +4613,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4644,11 +4652,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4678,14 +4686,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4717,11 +4725,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4739,7 +4747,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4751,14 +4759,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4790,7 +4798,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4824,14 +4832,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4863,11 +4871,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4885,7 +4893,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4897,12 +4905,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4970,14 +4978,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5009,7 +5017,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5043,12 +5051,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5116,14 +5124,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5146,7 +5154,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5154,10 +5162,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5166,41 +5172,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5234,9 +5238,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5266,14 +5270,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5296,7 +5300,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5304,8 +5308,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5314,39 +5320,41 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5378,11 +5386,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5412,14 +5420,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5453,9 +5461,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5485,12 +5493,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5558,14 +5566,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5597,11 +5605,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5631,12 +5639,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5704,14 +5712,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5743,11 +5751,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5777,12 +5785,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5850,14 +5858,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5889,11 +5897,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5923,12 +5931,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5966,7 +5974,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5996,12 +6004,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6069,14 +6077,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6108,11 +6116,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6142,12 +6150,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6203,7 +6211,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6215,14 +6223,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6254,11 +6262,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6288,12 +6296,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6329,9 +6337,9 @@
       <c r="I79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6349,7 +6357,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6361,14 +6369,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6400,7 +6408,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6434,14 +6442,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6473,11 +6481,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6507,14 +6515,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6548,9 +6556,9 @@
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6580,14 +6588,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6619,11 +6627,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6653,14 +6661,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6692,11 +6700,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6726,14 +6734,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6765,11 +6773,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6787,7 +6795,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6799,12 +6807,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6842,7 +6850,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6872,14 +6880,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6911,11 +6919,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6933,7 +6941,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6945,14 +6953,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6984,11 +6992,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7018,14 +7026,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7057,11 +7065,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7091,14 +7099,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7130,11 +7138,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7164,12 +7172,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7207,7 +7215,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7237,12 +7245,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7280,7 +7288,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7310,14 +7318,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7349,11 +7357,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7383,14 +7391,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7422,11 +7430,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7456,14 +7464,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7495,11 +7503,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7529,14 +7537,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7568,11 +7576,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7602,78 +7610,224 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-022-CZ</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Lixeira Preto com Cinza</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>5929841586</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>R$ 49,90</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,10 +674,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -686,39 +684,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +940,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1017,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1094,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1128,7 +1124,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1136,8 +1132,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1146,37 +1144,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1286,47 +1286,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1398,12 +1402,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1437,7 +1441,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1471,12 +1475,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1548,12 +1552,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1621,12 +1625,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1698,12 +1702,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1739,9 +1743,9 @@
       <c r="I17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1771,12 +1775,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1848,12 +1852,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1887,11 +1891,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1921,12 +1925,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1998,12 +2002,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2037,11 +2041,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2071,12 +2075,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2148,12 +2152,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2187,11 +2191,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2221,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2298,12 +2302,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2328,7 +2332,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2336,51 +2340,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2490,10 +2490,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2502,39 +2500,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2606,12 +2602,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2636,7 +2632,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2644,8 +2640,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2654,37 +2652,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2794,47 +2794,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2859,7 +2863,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2867,8 +2871,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2877,37 +2883,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2941,11 +2949,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2975,12 +2983,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3052,12 +3060,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3091,11 +3099,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3125,12 +3133,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3155,7 +3163,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3163,10 +3171,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3175,39 +3181,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3241,7 +3245,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3275,12 +3279,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3352,12 +3356,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3391,11 +3395,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3425,12 +3429,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3502,12 +3506,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3541,11 +3545,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3575,12 +3579,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3652,12 +3656,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3691,7 +3695,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3725,12 +3729,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3802,12 +3806,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3875,12 +3879,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3952,12 +3956,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3995,7 +3999,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -4025,12 +4029,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4102,12 +4106,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4141,11 +4145,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4175,12 +4179,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4205,7 +4209,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4213,8 +4217,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4223,37 +4229,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4287,11 +4295,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4321,12 +4329,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4351,7 +4359,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4359,47 +4367,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4433,11 +4445,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4467,12 +4479,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4506,7 +4518,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4540,12 +4552,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4579,11 +4591,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4613,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4686,12 +4698,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4725,11 +4737,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4759,12 +4771,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4832,12 +4844,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4871,11 +4883,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4893,7 +4905,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4905,12 +4917,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4946,9 +4958,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4978,12 +4990,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5017,7 +5029,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5051,12 +5063,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5090,7 +5102,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5124,12 +5136,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5165,9 +5177,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5185,7 +5197,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5197,12 +5209,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5270,12 +5282,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5300,7 +5312,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5308,10 +5320,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5320,39 +5330,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5388,9 +5396,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5420,12 +5428,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5493,12 +5501,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5532,11 +5540,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5566,12 +5574,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5596,7 +5604,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5604,47 +5612,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5678,11 +5690,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5712,12 +5724,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5751,11 +5763,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5785,12 +5797,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5858,12 +5870,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5897,11 +5909,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5931,12 +5943,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6004,12 +6016,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6045,9 +6057,9 @@
       <c r="I75" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6077,12 +6089,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6120,7 +6132,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6150,12 +6162,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6189,11 +6201,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6223,12 +6235,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6262,11 +6274,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6296,12 +6308,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6357,7 +6369,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6369,12 +6381,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6442,12 +6454,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6483,9 +6495,9 @@
       <c r="I81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6515,12 +6527,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6556,9 +6568,9 @@
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6588,12 +6600,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6627,11 +6639,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6649,7 +6661,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6661,12 +6673,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6700,11 +6712,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6734,12 +6746,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6777,7 +6789,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6807,12 +6819,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6846,11 +6858,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6880,12 +6892,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6919,11 +6931,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6941,7 +6953,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6953,12 +6965,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6992,11 +7004,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7026,12 +7038,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7065,11 +7077,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7099,12 +7111,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7138,11 +7150,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7172,12 +7184,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7211,11 +7223,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7233,7 +7245,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7245,12 +7257,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7284,11 +7296,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7318,12 +7330,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7357,11 +7369,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7391,12 +7403,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7430,11 +7442,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7464,12 +7476,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7503,11 +7515,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7537,12 +7549,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7576,11 +7588,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7610,12 +7622,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7683,12 +7695,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7756,78 +7768,370 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-022-CZ</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Lixeira Preto com Cinza</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>5929841586</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>R$ 49,90</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,8 +674,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>3</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -684,37 +686,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -863,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -940,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1017,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1094,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1124,7 +1128,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1132,10 +1136,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1144,39 +1146,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1475,12 +1475,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1585,9 +1585,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1625,12 +1625,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1702,12 +1702,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1741,24 +1741,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1852,12 +1852,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1891,11 +1891,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2002,12 +2002,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2041,11 +2041,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2525,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2948,8 +2948,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2958,37 +2960,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3060,12 +3064,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3090,7 +3094,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3098,47 +3102,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3163,7 +3171,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3171,8 +3179,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3181,37 +3191,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3245,11 +3257,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3279,12 +3291,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3356,12 +3368,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3395,11 +3407,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3429,12 +3441,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3506,12 +3518,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3545,11 +3557,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3579,12 +3591,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3656,12 +3668,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3695,11 +3707,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3729,12 +3741,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3806,12 +3818,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3845,11 +3857,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3879,12 +3891,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3956,12 +3968,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3995,11 +4007,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -4029,12 +4041,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4106,12 +4118,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4145,11 +4157,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4179,12 +4191,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4256,12 +4268,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4299,7 +4311,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4329,12 +4341,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4406,12 +4418,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4436,7 +4448,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4444,8 +4456,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>2</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4454,37 +4468,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4509,7 +4525,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4517,8 +4533,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4527,37 +4545,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4582,7 +4602,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4590,47 +4610,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4655,7 +4679,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4663,47 +4687,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4737,11 +4765,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4771,12 +4799,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4801,7 +4829,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4809,8 +4837,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>1</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4819,37 +4849,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4883,11 +4915,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4917,12 +4949,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4958,9 +4990,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4990,12 +5022,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5033,7 +5065,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5063,12 +5095,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5093,7 +5125,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5101,8 +5133,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>1</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5111,37 +5145,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5175,11 +5211,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5197,7 +5233,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5209,12 +5245,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5239,7 +5275,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5247,8 +5283,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5257,37 +5295,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5325,7 +5365,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5355,12 +5395,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5385,7 +5425,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5393,8 +5433,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5403,37 +5445,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5467,7 +5511,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5501,12 +5545,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5531,7 +5575,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5539,8 +5583,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5549,37 +5595,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5604,7 +5652,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5612,51 +5660,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5681,7 +5725,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5689,47 +5733,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5763,7 +5811,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5797,12 +5845,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5827,7 +5875,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5835,47 +5883,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>1</v>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5943,12 +5995,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5973,7 +6025,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5981,47 +6033,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>1</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6055,11 +6111,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6089,12 +6145,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6119,7 +6175,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6127,47 +6183,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>1</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6201,11 +6261,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6235,12 +6295,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6274,11 +6334,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6308,12 +6368,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6347,11 +6407,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6381,12 +6441,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6420,11 +6480,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6454,12 +6514,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6527,12 +6587,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6566,11 +6626,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6600,12 +6660,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6641,9 +6701,9 @@
       <c r="I83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6661,7 +6721,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6673,12 +6733,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6712,11 +6772,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6746,12 +6806,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6785,11 +6845,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6819,12 +6879,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6858,7 +6918,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6892,12 +6952,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6931,11 +6991,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6953,7 +7013,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6965,12 +7025,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7006,9 +7066,9 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7038,12 +7098,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7079,9 +7139,9 @@
       <c r="I89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7111,12 +7171,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7150,11 +7210,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7184,12 +7244,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7223,11 +7283,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7245,7 +7305,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7257,12 +7317,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7296,7 +7356,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7330,12 +7390,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7360,7 +7420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7368,47 +7428,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7476,12 +7540,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7515,11 +7579,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7549,12 +7613,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7622,12 +7686,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7661,11 +7725,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7695,12 +7759,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7738,7 +7802,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7768,12 +7832,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7807,11 +7871,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7841,12 +7905,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7880,11 +7944,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7914,12 +7978,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7953,11 +8017,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7987,12 +8051,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8030,7 +8094,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8060,78 +8124,1830 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-022-CZ</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Lixeira Preto com Cinza</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>5929841586</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>R$ 49,90</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1136,8 +1136,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1146,37 +1148,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1248,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1325,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1402,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1440,8 +1444,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1450,37 +1456,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1552,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1582,55 +1590,59 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1702,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1732,7 +1744,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1740,47 +1752,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1852,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1882,7 +1898,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1890,47 +1906,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2002,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2032,7 +2052,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2040,47 +2060,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>1</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2182,7 +2206,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2190,47 +2214,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2302,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2332,7 +2360,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2340,47 +2368,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,12 +2484,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2482,7 +2514,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2490,8 +2522,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>3</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2500,37 +2534,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,12 +2638,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2679,12 +2715,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2756,12 +2792,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2833,12 +2869,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2910,12 +2946,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2987,12 +3023,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3064,12 +3100,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3141,12 +3177,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3218,12 +3254,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3248,7 +3284,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3256,8 +3292,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3266,37 +3304,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3368,12 +3408,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3398,7 +3438,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3406,47 +3446,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3518,12 +3562,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3548,7 +3592,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3556,8 +3600,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>2</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3566,37 +3612,39 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3668,12 +3716,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3698,7 +3746,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3706,47 +3754,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3818,12 +3870,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3848,7 +3900,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3856,47 +3908,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3968,12 +4024,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3998,7 +4054,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4006,47 +4062,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>1</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4118,12 +4178,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4148,7 +4208,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4156,47 +4216,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4268,12 +4332,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4307,7 +4371,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4341,12 +4405,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4418,12 +4482,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4495,12 +4559,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4572,12 +4636,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4602,7 +4666,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4610,10 +4674,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4622,39 +4684,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4726,12 +4786,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,17 +4819,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4799,12 +4859,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4876,12 +4936,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4906,7 +4966,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4915,24 +4975,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4949,12 +5009,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4979,7 +5039,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4987,8 +5047,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4997,37 +5059,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5063,9 +5127,9 @@
       <c r="I61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5095,12 +5159,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5172,12 +5236,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5211,11 +5275,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5245,12 +5309,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5322,12 +5386,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5395,12 +5459,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5472,12 +5536,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5513,9 +5577,9 @@
       <c r="I67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5545,12 +5609,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5622,12 +5686,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5661,11 +5725,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5695,12 +5759,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5772,12 +5836,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5802,7 +5866,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5810,8 +5874,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>2</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5820,37 +5886,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5922,12 +5990,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5952,7 +6020,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5960,47 +6028,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6072,12 +6144,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6102,7 +6174,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6110,47 +6182,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>2</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6222,12 +6298,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6252,7 +6328,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6260,8 +6336,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>2</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6270,37 +6348,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6325,7 +6405,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6333,8 +6413,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6343,37 +6425,39 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6409,9 +6493,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6441,12 +6525,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6471,7 +6555,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6479,47 +6563,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6553,11 +6641,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6587,12 +6675,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6617,7 +6705,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6625,8 +6713,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>1</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6635,37 +6725,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6699,11 +6791,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6733,12 +6825,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6763,7 +6855,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6771,47 +6863,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6845,11 +6941,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6879,12 +6975,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6909,7 +7005,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6917,8 +7013,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>1</v>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6927,37 +7025,39 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6991,11 +7091,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7013,7 +7113,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -7025,12 +7125,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7055,7 +7155,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7063,8 +7163,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7073,37 +7175,39 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7141,7 +7245,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7171,12 +7275,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7201,7 +7305,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7209,8 +7313,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7219,37 +7325,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7283,11 +7391,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7317,12 +7425,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7347,7 +7455,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7355,8 +7463,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7365,37 +7475,39 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7420,7 +7532,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7428,10 +7540,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7440,39 +7550,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7497,7 +7605,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7505,47 +7613,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7570,7 +7682,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7578,8 +7690,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7588,37 +7702,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7643,7 +7759,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7651,47 +7767,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>1</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7716,7 +7836,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7724,47 +7844,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7789,7 +7913,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7797,47 +7921,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
-        <v>1</v>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7871,11 +7999,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7905,12 +8033,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7935,7 +8063,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7943,47 +8071,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
-        <v>1</v>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8017,11 +8149,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8051,12 +8183,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8090,11 +8222,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8124,12 +8256,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8163,7 +8295,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8197,12 +8329,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8227,7 +8359,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8235,8 +8367,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
-        <v>1</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8245,37 +8379,39 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8309,11 +8445,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8343,12 +8479,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8373,7 +8509,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8381,47 +8517,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8477,7 +8617,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
@@ -8489,12 +8629,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8519,7 +8659,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8527,8 +8667,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n">
-        <v>1</v>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8537,37 +8679,39 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8603,9 +8747,9 @@
       <c r="I109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8635,12 +8779,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8665,7 +8809,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8673,8 +8817,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="2" t="n">
-        <v>0</v>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8683,37 +8829,39 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8747,11 +8895,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8781,12 +8929,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8811,7 +8959,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8819,47 +8967,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8893,11 +9045,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8927,12 +9079,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8957,7 +9109,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8965,47 +9117,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
-        <v>2</v>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9039,11 +9195,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9061,7 +9217,7 @@
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
@@ -9073,12 +9229,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9103,7 +9259,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9111,8 +9267,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
-        <v>2</v>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9121,37 +9279,39 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9185,11 +9345,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9219,12 +9379,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9249,7 +9409,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9257,47 +9417,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9331,11 +9495,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9365,12 +9529,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9404,11 +9568,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9438,12 +9602,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9477,11 +9641,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9511,12 +9675,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9550,11 +9714,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9584,12 +9748,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9623,11 +9787,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9657,12 +9821,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9696,11 +9860,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9730,12 +9894,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9771,9 +9935,9 @@
       <c r="I125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9803,12 +9967,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9842,11 +10006,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9876,12 +10040,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9915,7 +10079,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9937,17 +10101,3087 @@
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4255,12 +4255,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4332,14 +4332,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4370,8 +4370,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4380,37 +4382,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4482,14 +4486,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4512,7 +4516,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4520,10 +4524,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4532,39 +4534,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4636,14 +4636,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4674,8 +4674,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4684,37 +4686,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4786,14 +4790,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4819,17 +4823,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4859,12 +4863,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4936,14 +4940,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4966,33 +4970,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5009,12 +5013,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5086,14 +5090,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5116,7 +5120,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5125,24 +5129,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5159,12 +5163,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5236,14 +5240,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5275,11 +5279,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5309,12 +5313,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5386,12 +5390,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5459,12 +5463,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5536,12 +5540,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5577,9 +5581,9 @@
       <c r="I67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5609,12 +5613,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5686,14 +5690,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5725,11 +5729,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5759,12 +5763,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5836,14 +5840,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5866,7 +5870,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5874,10 +5878,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5886,39 +5888,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6452,14 +6452,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6490,8 +6490,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6500,37 +6502,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6602,12 +6606,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6643,9 +6647,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6675,12 +6679,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6752,14 +6756,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6791,11 +6795,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6825,12 +6829,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6902,14 +6906,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6941,11 +6945,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6975,12 +6979,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7052,14 +7056,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7091,11 +7095,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7125,12 +7129,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7202,14 +7206,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7241,11 +7245,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7275,12 +7279,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7352,12 +7356,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7393,9 +7397,9 @@
       <c r="I91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7425,12 +7429,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7502,14 +7506,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7541,11 +7545,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7575,12 +7579,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7652,14 +7656,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7682,7 +7686,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7690,10 +7694,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7702,39 +7704,37 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7960,14 +7960,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7998,8 +7998,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -8008,37 +8010,39 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8110,12 +8114,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8151,9 +8155,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8183,14 +8187,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8213,7 +8217,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8221,8 +8225,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="2" t="n">
-        <v>0</v>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8231,39 +8237,41 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8295,11 +8303,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8329,14 +8337,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8359,7 +8367,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8367,10 +8375,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8379,39 +8385,37 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8447,9 +8451,9 @@
       <c r="I105" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8479,12 +8483,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8556,14 +8560,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8595,11 +8599,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8629,12 +8633,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8706,12 +8710,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8749,7 +8753,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8779,12 +8783,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8856,14 +8860,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8895,11 +8899,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8929,12 +8933,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9006,14 +9010,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9045,11 +9049,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -9079,12 +9083,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9156,14 +9160,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9195,11 +9199,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9229,12 +9233,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9306,14 +9310,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9345,11 +9349,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9379,12 +9383,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9456,12 +9460,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9499,7 +9503,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9529,14 +9533,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9559,7 +9563,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9567,8 +9571,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" s="2" t="n">
-        <v>0</v>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -9577,39 +9583,41 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9641,11 +9649,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9675,12 +9683,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9716,9 +9724,9 @@
       <c r="I122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9748,14 +9756,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9787,11 +9795,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9821,14 +9829,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9860,11 +9868,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9894,12 +9902,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9935,9 +9943,9 @@
       <c r="I125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9967,14 +9975,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10006,11 +10014,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -10040,14 +10048,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10079,11 +10087,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -10113,14 +10121,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10152,11 +10160,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10186,14 +10194,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10225,11 +10233,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10247,7 +10255,7 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
@@ -10259,14 +10267,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10298,7 +10306,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10332,14 +10340,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10371,11 +10379,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10393,7 +10401,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10405,12 +10413,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10478,14 +10486,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10517,7 +10525,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10551,12 +10559,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10624,14 +10632,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10654,7 +10662,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10662,10 +10670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10674,39 +10680,37 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10742,9 +10746,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10774,14 +10778,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10804,7 +10808,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10812,8 +10816,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>0</v>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10822,39 +10828,41 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10886,11 +10894,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10920,12 +10928,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10961,9 +10969,9 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10993,12 +11001,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11066,14 +11074,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11105,11 +11113,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11139,12 +11147,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11212,14 +11220,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11251,11 +11259,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11285,12 +11293,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11358,14 +11366,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11397,11 +11405,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11431,12 +11439,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11474,7 +11482,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11504,12 +11512,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11577,14 +11585,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11616,11 +11624,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11650,12 +11658,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11711,7 +11719,7 @@
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
@@ -11723,14 +11731,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11762,11 +11770,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11796,12 +11804,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11837,9 +11845,9 @@
       <c r="I151" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11857,7 +11865,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11869,14 +11877,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11908,7 +11916,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -11942,14 +11950,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11981,11 +11989,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -12015,12 +12023,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12056,9 +12064,9 @@
       <c r="I154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -12088,14 +12096,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12127,11 +12135,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12161,14 +12169,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12200,11 +12208,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12234,14 +12242,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12273,11 +12281,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12295,7 +12303,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -12307,12 +12315,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12350,7 +12358,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12380,14 +12388,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12419,11 +12427,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12441,7 +12449,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -12453,14 +12461,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12492,11 +12500,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12526,14 +12534,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12565,11 +12573,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12599,14 +12607,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12638,11 +12646,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12672,12 +12680,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12715,7 +12723,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12745,12 +12753,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12788,7 +12796,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12818,14 +12826,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12857,11 +12865,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12891,14 +12899,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12930,11 +12938,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12964,14 +12972,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13003,11 +13011,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -13037,14 +13045,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13076,11 +13084,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13110,14 +13118,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13149,7 +13157,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -13171,17 +13179,163 @@
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="O170" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4255,12 +4255,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4486,14 +4486,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4524,8 +4524,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4534,37 +4536,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4636,14 +4640,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4666,7 +4670,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4674,10 +4678,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4686,39 +4688,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4790,14 +4790,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4828,8 +4828,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4838,37 +4840,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4940,14 +4944,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4973,17 +4977,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -5013,12 +5017,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5090,14 +5094,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5120,33 +5124,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5163,12 +5167,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5240,14 +5244,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5270,7 +5274,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5279,24 +5283,24 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5313,12 +5317,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5390,14 +5394,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5429,11 +5433,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5463,12 +5467,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5540,12 +5544,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5613,12 +5617,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5690,12 +5694,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5731,9 +5735,9 @@
       <c r="I69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5763,12 +5767,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5840,14 +5844,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5879,11 +5883,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5913,12 +5917,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5990,14 +5994,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6020,7 +6024,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -6028,10 +6032,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -6040,39 +6042,37 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6606,14 +6606,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6644,8 +6644,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6654,37 +6656,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6756,12 +6760,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6797,9 +6801,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6829,12 +6833,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6906,14 +6910,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6945,11 +6949,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6979,12 +6983,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7056,14 +7060,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7095,11 +7099,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7129,12 +7133,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7206,14 +7210,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7245,11 +7249,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7279,12 +7283,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7356,14 +7360,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7395,11 +7399,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7429,12 +7433,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7506,12 +7510,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7547,9 +7551,9 @@
       <c r="I93" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7579,12 +7583,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7656,14 +7660,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7695,11 +7699,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7729,12 +7733,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7806,14 +7810,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7836,7 +7840,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7844,10 +7848,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7856,39 +7858,37 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8114,14 +8114,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8152,8 +8152,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -8162,37 +8164,39 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8264,12 +8268,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8305,9 +8309,9 @@
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8337,14 +8341,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8367,7 +8371,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8375,8 +8379,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
-        <v>0</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8385,39 +8391,41 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8449,11 +8457,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8483,14 +8491,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8513,7 +8521,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8521,10 +8529,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8533,39 +8539,37 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8601,9 +8605,9 @@
       <c r="I107" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8633,12 +8637,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8710,14 +8714,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8749,11 +8753,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8783,12 +8787,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8860,12 +8864,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8903,7 +8907,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8933,12 +8937,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9010,14 +9014,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9049,11 +9053,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -9083,12 +9087,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9160,14 +9164,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9199,11 +9203,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9233,12 +9237,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9310,14 +9314,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9349,11 +9353,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9383,12 +9387,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9460,14 +9464,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9499,11 +9503,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9533,12 +9537,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9610,12 +9614,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9653,7 +9657,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9683,14 +9687,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9713,7 +9717,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9721,8 +9725,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="n">
-        <v>0</v>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9731,39 +9737,41 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9795,11 +9803,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9829,12 +9837,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9870,9 +9878,9 @@
       <c r="I124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9902,14 +9910,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9941,11 +9949,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9975,14 +9983,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10014,11 +10022,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -10048,12 +10056,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10089,9 +10097,9 @@
       <c r="I127" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -10121,14 +10129,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10160,11 +10168,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10194,14 +10202,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10233,11 +10241,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10267,14 +10275,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10306,11 +10314,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10340,14 +10348,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10379,11 +10387,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10401,7 +10409,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10413,14 +10421,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10452,7 +10460,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10486,14 +10494,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10525,11 +10533,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10547,7 +10555,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10559,12 +10567,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10632,14 +10640,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10671,7 +10679,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10705,12 +10713,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10778,14 +10786,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10808,7 +10816,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10816,10 +10824,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10828,39 +10834,37 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10896,9 +10900,9 @@
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10928,14 +10932,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10958,7 +10962,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10966,8 +10970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10976,39 +10982,41 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11040,11 +11048,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -11074,12 +11082,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11115,9 +11123,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11147,12 +11155,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11220,14 +11228,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11259,11 +11267,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11293,12 +11301,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11366,14 +11374,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11405,11 +11413,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11439,12 +11447,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11512,14 +11520,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11551,11 +11559,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11585,12 +11593,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11628,7 +11636,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11658,12 +11666,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11731,14 +11739,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11770,11 +11778,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11804,12 +11812,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11865,7 +11873,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11877,14 +11885,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11916,11 +11924,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11950,12 +11958,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11991,9 +11999,9 @@
       <c r="I153" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -12011,7 +12019,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -12023,14 +12031,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12062,7 +12070,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -12096,14 +12104,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12135,11 +12143,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12169,12 +12177,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12210,9 +12218,9 @@
       <c r="I156" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12242,14 +12250,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12281,11 +12289,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12315,14 +12323,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12354,11 +12362,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12388,14 +12396,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12427,11 +12435,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12449,7 +12457,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -12461,12 +12469,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12504,7 +12512,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12534,14 +12542,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12573,11 +12581,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12595,7 +12603,7 @@
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12607,14 +12615,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12646,11 +12654,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12680,14 +12688,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12719,11 +12727,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12753,14 +12761,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12792,11 +12800,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12826,12 +12834,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12869,7 +12877,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12899,12 +12907,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12942,7 +12950,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12972,14 +12980,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13011,11 +13019,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -13045,14 +13053,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13084,11 +13092,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13118,14 +13126,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13157,11 +13165,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13191,14 +13199,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13230,11 +13238,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13264,14 +13272,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13303,7 +13311,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -13325,17 +13333,163 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="O172" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4255,12 +4255,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4640,14 +4640,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4678,8 +4678,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4688,37 +4690,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4790,14 +4794,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4820,7 +4824,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4828,10 +4832,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4840,39 +4842,37 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4944,14 +4944,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4982,8 +4982,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4992,37 +4994,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5094,14 +5098,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5127,17 +5131,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5167,12 +5171,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5244,14 +5248,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5274,33 +5278,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5317,12 +5321,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5394,14 +5398,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5424,7 +5428,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5433,24 +5437,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5467,12 +5471,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5544,14 +5548,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -5583,11 +5587,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5617,12 +5621,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5694,12 +5698,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5767,12 +5771,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5844,12 +5848,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5885,9 +5889,9 @@
       <c r="I71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5917,12 +5921,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5994,14 +5998,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6033,11 +6037,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -6067,12 +6071,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6144,14 +6148,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6174,7 +6178,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6182,10 +6186,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6194,39 +6196,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6760,14 +6760,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6798,8 +6798,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6808,37 +6810,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6910,12 +6914,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6951,9 +6955,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6983,12 +6987,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7060,14 +7064,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7099,11 +7103,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7133,12 +7137,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7210,14 +7214,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7249,11 +7253,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7283,12 +7287,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7360,14 +7364,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7399,11 +7403,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7433,12 +7437,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7510,14 +7514,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7549,11 +7553,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7583,12 +7587,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7660,12 +7664,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7701,9 +7705,9 @@
       <c r="I95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7733,12 +7737,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7810,14 +7814,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7849,11 +7853,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7883,12 +7887,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7960,14 +7964,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -7990,7 +7994,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7998,10 +8002,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -8010,39 +8012,37 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8268,14 +8268,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8306,8 +8306,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
-        <v>0</v>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8316,37 +8318,39 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8418,12 +8422,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8459,9 +8463,9 @@
       <c r="I105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8491,14 +8495,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8521,7 +8525,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8529,8 +8533,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="n">
-        <v>0</v>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8539,39 +8545,41 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8603,11 +8611,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8637,14 +8645,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8667,7 +8675,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8675,10 +8683,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8687,39 +8693,37 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8755,9 +8759,9 @@
       <c r="I109" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8787,12 +8791,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8864,14 +8868,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -8903,11 +8907,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8937,12 +8941,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9014,12 +9018,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9057,7 +9061,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -9087,12 +9091,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9164,14 +9168,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9203,11 +9207,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9237,12 +9241,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9314,14 +9318,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9353,11 +9357,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9387,12 +9391,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9464,14 +9468,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9503,11 +9507,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9537,12 +9541,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9614,14 +9618,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9653,11 +9657,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9687,12 +9691,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9764,12 +9768,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9807,7 +9811,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9837,14 +9841,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9867,7 +9871,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9875,8 +9879,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9885,39 +9891,41 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -9949,11 +9957,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9983,12 +9991,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10024,9 +10032,9 @@
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -10056,14 +10064,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10095,11 +10103,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -10129,14 +10137,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10168,11 +10176,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10202,12 +10210,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10243,9 +10251,9 @@
       <c r="I129" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10275,14 +10283,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10314,11 +10322,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10348,14 +10356,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10387,11 +10395,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10421,14 +10429,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10460,11 +10468,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10494,14 +10502,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10533,11 +10541,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10555,7 +10563,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10567,14 +10575,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10606,7 +10614,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10640,14 +10648,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10679,11 +10687,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10701,7 +10709,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10713,12 +10721,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10786,14 +10794,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10825,7 +10833,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10859,12 +10867,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10932,14 +10940,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -10962,7 +10970,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10970,10 +10978,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10982,39 +10988,37 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11050,9 +11054,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -11082,14 +11086,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11112,7 +11116,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11120,8 +11124,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11130,39 +11136,41 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11194,11 +11202,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11228,12 +11236,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11269,9 +11277,9 @@
       <c r="I143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11301,12 +11309,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11374,14 +11382,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11413,11 +11421,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11447,12 +11455,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11520,14 +11528,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11559,11 +11567,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11593,12 +11601,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11666,14 +11674,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11705,11 +11713,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11739,12 +11747,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11782,7 +11790,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11812,12 +11820,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11885,14 +11893,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -11924,11 +11932,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11958,12 +11966,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12019,7 +12027,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -12031,14 +12039,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12070,11 +12078,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -12104,12 +12112,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12145,9 +12153,9 @@
       <c r="I155" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12165,7 +12173,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -12177,14 +12185,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12216,7 +12224,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -12250,14 +12258,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12289,11 +12297,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12323,12 +12331,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12364,9 +12372,9 @@
       <c r="I158" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12396,14 +12404,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12435,11 +12443,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12469,14 +12477,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12508,11 +12516,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12542,14 +12550,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12581,11 +12589,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12603,7 +12611,7 @@
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12615,12 +12623,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12658,7 +12666,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12688,14 +12696,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12727,11 +12735,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12749,7 +12757,7 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12761,14 +12769,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12800,11 +12808,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12834,14 +12842,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12873,11 +12881,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12907,14 +12915,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -12946,11 +12954,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12980,12 +12988,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13023,7 +13031,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -13053,12 +13061,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13096,7 +13104,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13126,14 +13134,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13165,11 +13173,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13199,14 +13207,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13238,11 +13246,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13272,14 +13280,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13311,11 +13319,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13345,14 +13353,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13384,11 +13392,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13418,14 +13426,14 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
           <t>UTD-022-CZ</t>
@@ -13457,7 +13465,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
@@ -13479,17 +13487,163 @@
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="O174" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-022-CZ-LIXEIRA-PRETO-COM-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,51 +597,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -743,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -751,10 +747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -763,39 +757,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1013,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1090,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1167,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1244,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1321,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1398,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1475,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1552,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1629,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1706,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1783,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1860,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1937,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2014,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2091,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2168,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2245,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2322,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,12 +2399,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2484,12 +2476,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2561,12 +2553,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2638,12 +2630,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2715,12 +2707,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2792,12 +2784,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2869,12 +2861,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2946,12 +2938,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3023,12 +3015,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3100,12 +3092,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3177,12 +3169,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3254,12 +3246,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3331,12 +3323,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3408,12 +3400,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3485,12 +3477,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3562,12 +3554,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3639,12 +3631,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3716,12 +3708,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3793,12 +3785,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3870,12 +3862,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3947,12 +3939,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4024,12 +4016,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4101,12 +4093,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4178,12 +4170,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4255,12 +4247,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4332,12 +4324,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4409,12 +4401,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4486,12 +4478,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4563,12 +4555,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4640,12 +4632,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4717,12 +4709,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4794,12 +4786,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4824,7 +4816,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4832,8 +4824,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4842,37 +4836,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4944,12 +4940,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5021,12 +5017,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5098,12 +5094,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5128,7 +5124,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5136,8 +5132,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5146,37 +5144,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5278,55 +5278,59 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5398,12 +5402,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5428,7 +5432,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5437,24 +5441,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5471,12 +5475,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5548,12 +5552,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5578,7 +5582,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5586,47 +5590,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5698,12 +5706,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5737,11 +5745,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5771,12 +5779,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5848,12 +5856,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5881,17 +5889,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5921,12 +5929,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5998,12 +6006,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6028,7 +6036,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -6041,20 +6049,20 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6071,12 +6079,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6148,12 +6156,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6187,11 +6195,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6221,12 +6229,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6298,12 +6306,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6328,7 +6336,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6336,51 +6344,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6452,12 +6456,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6482,7 +6486,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6490,51 +6494,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6644,51 +6644,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6760,12 +6756,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6790,7 +6786,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6798,10 +6794,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6810,39 +6804,37 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6914,12 +6906,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6944,7 +6936,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6952,8 +6944,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6962,37 +6956,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7064,12 +7060,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7094,7 +7090,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -7102,47 +7098,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7252,8 +7252,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>2</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7262,37 +7264,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7364,12 +7368,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7394,7 +7398,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7402,47 +7406,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7514,12 +7522,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7553,11 +7561,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7587,12 +7595,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7664,12 +7672,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7703,11 +7711,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7737,12 +7745,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7814,12 +7822,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7853,11 +7861,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7887,12 +7895,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7964,12 +7972,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8003,11 +8011,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -8037,12 +8045,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8114,12 +8122,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8144,7 +8152,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8152,51 +8160,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8268,12 +8272,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8298,7 +8302,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8306,51 +8310,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8461,11 +8461,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8572,12 +8572,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8611,11 +8611,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8683,8 +8683,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8693,37 +8695,39 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8748,7 +8752,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8756,47 +8760,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>2</v>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8868,12 +8876,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8898,7 +8906,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8906,47 +8914,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9018,12 +9030,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9057,11 +9069,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -9091,12 +9103,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9168,12 +9180,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9207,11 +9219,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9241,12 +9253,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9271,7 +9283,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9279,10 +9291,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9291,39 +9301,37 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9357,11 +9365,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9391,12 +9399,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9468,12 +9476,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9509,9 +9517,9 @@
       <c r="I119" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9541,12 +9549,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9618,12 +9626,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9657,11 +9665,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9691,12 +9699,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9768,12 +9776,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9807,11 +9815,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9841,12 +9849,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9918,12 +9926,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9957,11 +9965,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9991,12 +9999,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10021,7 +10029,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -10029,8 +10037,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="n">
-        <v>0</v>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -10039,37 +10049,39 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10103,11 +10115,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -10137,12 +10149,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10167,7 +10179,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -10175,47 +10187,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10249,11 +10265,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10283,12 +10299,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10313,7 +10329,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10321,8 +10337,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I130" s="2" t="n">
-        <v>1</v>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10331,37 +10349,39 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10395,11 +10415,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10429,12 +10449,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10459,7 +10479,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10467,47 +10487,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10575,12 +10599,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10614,7 +10638,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10648,12 +10672,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10709,7 +10733,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10721,12 +10745,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10762,9 +10786,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10794,12 +10818,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10837,7 +10861,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10867,12 +10891,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10906,7 +10930,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10940,12 +10964,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10979,11 +11003,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -11013,12 +11037,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11054,9 +11078,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -11086,12 +11110,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11116,7 +11140,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11124,10 +11148,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I141" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11136,39 +11158,37 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11202,11 +11222,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11236,12 +11256,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11277,9 +11297,9 @@
       <c r="I143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11297,7 +11317,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
@@ -11309,12 +11329,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11348,11 +11368,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11382,12 +11402,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11421,11 +11441,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11455,12 +11475,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11494,11 +11514,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11528,12 +11548,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11567,11 +11587,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11601,12 +11621,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11640,11 +11660,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11674,12 +11694,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11704,7 +11724,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11712,47 +11732,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11786,11 +11810,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11820,12 +11844,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11859,11 +11883,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11893,12 +11917,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11936,7 +11960,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11966,12 +11990,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12005,11 +12029,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -12039,12 +12063,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12078,11 +12102,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -12112,12 +12136,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12153,9 +12177,9 @@
       <c r="I155" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12173,7 +12197,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -12185,12 +12209,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12228,7 +12252,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12258,12 +12282,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12297,11 +12321,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12331,12 +12355,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12370,11 +12394,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12404,12 +12428,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12443,11 +12467,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12477,12 +12501,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12516,11 +12540,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12550,12 +12574,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12591,9 +12615,9 @@
       <c r="I161" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12623,12 +12647,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12662,11 +12686,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12696,12 +12720,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12735,11 +12759,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12769,12 +12793,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12808,7 +12832,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -12842,12 +12866,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12881,11 +12905,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12915,12 +12939,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12956,9 +12980,9 @@
       <c r="I166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12988,12 +13012,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13027,11 +13051,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -13061,12 +13085,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13100,11 +13124,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13134,12 +13158,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13175,9 +13199,9 @@
       <c r="I169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13207,12 +13231,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13246,11 +13270,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13280,12 +13304,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13319,11 +13343,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13341,7 +13365,7 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -13353,12 +13377,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13392,11 +13416,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13426,12 +13450,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13465,11 +13489,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13499,12 +13523,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13538,11 +13562,11 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13572,12 +13596,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -13611,11 +13635,11 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -13633,17 +13657,601 @@
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O176" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>5471866994</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 37,42</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-022-CZ</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Lixeira Preto com Cinza</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>5929841586</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>